--- a/artfynd/A 57844-2022 artfynd.xlsx
+++ b/artfynd/A 57844-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57844-2022 artfynd.xlsx
+++ b/artfynd/A 57844-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2290,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112678693</v>
+        <v>112678620</v>
       </c>
       <c r="B17" t="n">
-        <v>95977</v>
+        <v>95225</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2306,21 +2306,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221944</v>
+        <v>2326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,13 +2330,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527240</v>
+        <v>527136</v>
       </c>
       <c r="R17" t="n">
-        <v>7101112</v>
+        <v>7101176</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2397,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112678620</v>
+        <v>112678615</v>
       </c>
       <c r="B18" t="n">
-        <v>95225</v>
+        <v>89792</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2409,25 +2409,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2326</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527136</v>
+        <v>527050</v>
       </c>
       <c r="R18" t="n">
-        <v>7101176</v>
+        <v>7101228</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2475,6 +2475,11 @@
           <t>2023-10-06</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Strandskogen, i kanten av planerad hänsyn</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2486,7 +2491,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+          <t>Äldre barrskog vid sjöstrand med lövinslag och med en del död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2504,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112678615</v>
+        <v>112678595</v>
       </c>
       <c r="B19" t="n">
-        <v>89792</v>
+        <v>93675</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2516,25 +2521,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>210</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527050</v>
+        <v>527150</v>
       </c>
       <c r="R19" t="n">
-        <v>7101228</v>
+        <v>7101330</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2589,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Strandskogen, i kanten av planerad hänsyn</t>
+          <t>Protonema</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2598,7 +2603,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Äldre barrskog vid sjöstrand med lövinslag och med en del död ved i olika nedbrytningsstadier</t>
+          <t>Äldre barrskog vid sjöstrand med blöthål och med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2616,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112678595</v>
+        <v>112678701</v>
       </c>
       <c r="B20" t="n">
-        <v>93675</v>
+        <v>94580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2628,25 +2633,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2661,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527150</v>
+        <v>527226</v>
       </c>
       <c r="R20" t="n">
-        <v>7101330</v>
+        <v>7101137</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,11 +2699,6 @@
           <t>2023-10-06</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Protonema</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Äldre barrskog vid sjöstrand med blöthål och med död ved i olika nedbrytningsstadier</t>
+          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2728,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112678701</v>
+        <v>112678705</v>
       </c>
       <c r="B21" t="n">
-        <v>94580</v>
+        <v>56641</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2744,21 +2744,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527226</v>
+        <v>527223</v>
       </c>
       <c r="R21" t="n">
         <v>7101137</v>
@@ -2804,6 +2804,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spår i gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,10 +2840,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112678705</v>
+        <v>112678596</v>
       </c>
       <c r="B22" t="n">
-        <v>56641</v>
+        <v>74065</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2851,21 +2856,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2875,10 +2880,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527223</v>
+        <v>527150</v>
       </c>
       <c r="R22" t="n">
-        <v>7101137</v>
+        <v>7101330</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,11 +2918,6 @@
           <t>2023-10-06</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spår i gran</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2929,7 +2929,12 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+          <t>Äldre barrskog vid sjöstrand med blöthål och med död ved i olika nedbrytningsstadier</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Vid basen av nydöd gran, 15 cm.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -2947,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112678596</v>
+        <v>112678685</v>
       </c>
       <c r="B23" t="n">
-        <v>74065</v>
+        <v>93478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2959,25 +2964,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1467</v>
+        <v>2809</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2987,10 +2992,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527150</v>
+        <v>527294</v>
       </c>
       <c r="R23" t="n">
-        <v>7101330</v>
+        <v>7101096</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,12 +3041,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Äldre barrskog vid sjöstrand med blöthål och med död ved i olika nedbrytningsstadier</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Vid basen av nydöd gran, 15 cm.</t>
+          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112678685</v>
+        <v>112678667</v>
       </c>
       <c r="B24" t="n">
-        <v>93478</v>
+        <v>89814</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3071,25 +3071,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3099,10 +3099,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527294</v>
+        <v>527202</v>
       </c>
       <c r="R24" t="n">
-        <v>7101096</v>
+        <v>7101154</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3166,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112678667</v>
+        <v>112678695</v>
       </c>
       <c r="B25" t="n">
-        <v>89814</v>
+        <v>89760</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3178,25 +3178,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527202</v>
+        <v>527240</v>
       </c>
       <c r="R25" t="n">
-        <v>7101154</v>
+        <v>7101112</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3273,10 +3273,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112678695</v>
+        <v>112678664</v>
       </c>
       <c r="B26" t="n">
-        <v>89760</v>
+        <v>89814</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3285,25 +3285,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527240</v>
+        <v>527186</v>
       </c>
       <c r="R26" t="n">
-        <v>7101112</v>
+        <v>7101165</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3380,10 +3380,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112678664</v>
+        <v>112678680</v>
       </c>
       <c r="B27" t="n">
-        <v>89814</v>
+        <v>74060</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3396,21 +3396,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527186</v>
+        <v>527322</v>
       </c>
       <c r="R27" t="n">
-        <v>7101165</v>
+        <v>7101080</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112678680</v>
+        <v>112678671</v>
       </c>
       <c r="B28" t="n">
-        <v>74060</v>
+        <v>93675</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3499,25 +3499,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>210</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3527,10 +3527,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527322</v>
+        <v>527236</v>
       </c>
       <c r="R28" t="n">
-        <v>7101080</v>
+        <v>7101138</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3565,6 +3565,11 @@
           <t>2023-10-06</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Protonema</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3577,6 +3582,21 @@
       <c r="AI28" t="inlineStr">
         <is>
           <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Murken granlåga</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>23-537</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3594,10 +3614,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112678671</v>
+        <v>112678689</v>
       </c>
       <c r="B29" t="n">
-        <v>93675</v>
+        <v>94900</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3606,25 +3626,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>210</v>
+        <v>1841</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3634,10 +3654,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527236</v>
+        <v>527260</v>
       </c>
       <c r="R29" t="n">
-        <v>7101138</v>
+        <v>7101099</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3674,7 +3694,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Protonema</t>
+          <t>Delvis utanför skyddszonen</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3693,17 +3713,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Murken granlåga</t>
-        </is>
-      </c>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>23-537</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3721,10 +3731,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112678689</v>
+        <v>112678645</v>
       </c>
       <c r="B30" t="n">
-        <v>94900</v>
+        <v>93478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3733,25 +3743,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1841</v>
+        <v>2809</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3761,13 +3771,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527260</v>
+        <v>527136</v>
       </c>
       <c r="R30" t="n">
-        <v>7101099</v>
+        <v>7101176</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3799,11 +3809,6 @@
           <t>2023-10-06</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Delvis utanför skyddszonen</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3816,11 +3821,6 @@
       <c r="AI30" t="inlineStr">
         <is>
           <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3838,10 +3838,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112678645</v>
+        <v>112678675</v>
       </c>
       <c r="B31" t="n">
-        <v>93478</v>
+        <v>94900</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3850,25 +3850,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2809</v>
+        <v>1841</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3878,13 +3878,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527136</v>
+        <v>527289</v>
       </c>
       <c r="R31" t="n">
-        <v>7101176</v>
+        <v>7101110</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3945,10 +3945,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112678675</v>
+        <v>112678597</v>
       </c>
       <c r="B32" t="n">
-        <v>94900</v>
+        <v>93596</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3961,34 +3961,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1841</v>
+        <v>771</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Platt spretmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Herzogiella turfacea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Lindb.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gårdsvattnet SO, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527289</v>
+        <v>527150</v>
       </c>
       <c r="R32" t="n">
-        <v>7101110</v>
+        <v>7101330</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4034,7 +4039,22 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+          <t>Äldre barrskog vid sjöstrand med blöthål och med död ved i olika nedbrytningsstadier</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>På granstubbe och lövved i blöthål några meter innanför stranden</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>23-538</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4052,10 +4072,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112678597</v>
+        <v>112678604</v>
       </c>
       <c r="B33" t="n">
-        <v>93596</v>
+        <v>77876</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4068,39 +4088,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>771</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Platt spretmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Herzogiella turfacea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lindb.) Z.Iwats.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gårdsvattnet SO, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527150</v>
+        <v>527256</v>
       </c>
       <c r="R33" t="n">
-        <v>7101330</v>
+        <v>7101242</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4146,22 +4161,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Äldre barrskog vid sjöstrand med blöthål och med död ved i olika nedbrytningsstadier</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>På granstubbe och lövved i blöthål några meter innanför stranden</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>23-538</t>
+          <t>Äldre granskog med stort lövinslag intill bäck</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4179,7 +4179,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112678604</v>
+        <v>112678668</v>
       </c>
       <c r="B34" t="n">
         <v>77876</v>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527256</v>
+        <v>527236</v>
       </c>
       <c r="R34" t="n">
-        <v>7101242</v>
+        <v>7101138</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Äldre granskog med stort lövinslag intill bäck</t>
+          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4286,7 +4286,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112678668</v>
+        <v>112678709</v>
       </c>
       <c r="B35" t="n">
         <v>77876</v>
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527236</v>
+        <v>527172</v>
       </c>
       <c r="R35" t="n">
-        <v>7101138</v>
+        <v>7101167</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112678709</v>
+        <v>112678707</v>
       </c>
       <c r="B36" t="n">
-        <v>77876</v>
+        <v>93490</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4405,25 +4405,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>527172</v>
+        <v>527205</v>
       </c>
       <c r="R36" t="n">
-        <v>7101167</v>
+        <v>7101146</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4500,10 +4500,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112678707</v>
+        <v>112678628</v>
       </c>
       <c r="B37" t="n">
-        <v>93490</v>
+        <v>94900</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4512,25 +4512,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2813</v>
+        <v>1841</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4540,13 +4540,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527205</v>
+        <v>527136</v>
       </c>
       <c r="R37" t="n">
-        <v>7101146</v>
+        <v>7101176</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4607,10 +4607,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112678628</v>
+        <v>112678606</v>
       </c>
       <c r="B38" t="n">
-        <v>94900</v>
+        <v>89760</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4619,25 +4619,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1841</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4647,13 +4647,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527136</v>
+        <v>527218</v>
       </c>
       <c r="R38" t="n">
-        <v>7101176</v>
+        <v>7101268</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+          <t>Äldre granskog med stort lövinslag intill bäck</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4714,10 +4714,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112678606</v>
+        <v>112678712</v>
       </c>
       <c r="B39" t="n">
-        <v>89760</v>
+        <v>104065</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4730,21 +4730,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527218</v>
+        <v>527096</v>
       </c>
       <c r="R39" t="n">
-        <v>7101268</v>
+        <v>7101170</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Äldre granskog med stort lövinslag intill bäck</t>
+          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112678712</v>
+        <v>112678612</v>
       </c>
       <c r="B40" t="n">
-        <v>104065</v>
+        <v>77876</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4833,25 +4833,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527096</v>
+        <v>527045</v>
       </c>
       <c r="R40" t="n">
-        <v>7101170</v>
+        <v>7101241</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+          <t>Äldre barrskog vid sjöstrand med lövinslag och med en del död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -4928,7 +4928,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112678612</v>
+        <v>112678711</v>
       </c>
       <c r="B41" t="n">
         <v>77876</v>
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527045</v>
+        <v>527144</v>
       </c>
       <c r="R41" t="n">
-        <v>7101241</v>
+        <v>7101152</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Äldre barrskog vid sjöstrand med lövinslag och med en del död ved i olika nedbrytningsstadier</t>
+          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5035,10 +5035,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112678711</v>
+        <v>112678607</v>
       </c>
       <c r="B42" t="n">
-        <v>77876</v>
+        <v>93478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5047,25 +5047,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527144</v>
+        <v>527218</v>
       </c>
       <c r="R42" t="n">
-        <v>7101152</v>
+        <v>7101268</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+          <t>Äldre granskog med stort lövinslag intill bäck</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5142,10 +5142,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112678607</v>
+        <v>112678646</v>
       </c>
       <c r="B43" t="n">
-        <v>93478</v>
+        <v>93477</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5158,21 +5158,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2809</v>
+        <v>2808</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Grov husmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hylocomiastrum pyrenaicum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spruce) M.Fleisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5182,13 +5182,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527218</v>
+        <v>527136</v>
       </c>
       <c r="R43" t="n">
-        <v>7101268</v>
+        <v>7101176</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Äldre granskog med stort lövinslag intill bäck</t>
+          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5249,10 +5249,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112678646</v>
+        <v>112678602</v>
       </c>
       <c r="B44" t="n">
-        <v>93477</v>
+        <v>77876</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5261,25 +5261,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2808</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grov husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hylocomiastrum pyrenaicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spruce) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5289,13 +5289,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527136</v>
+        <v>527212</v>
       </c>
       <c r="R44" t="n">
-        <v>7101176</v>
+        <v>7101308</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+          <t>Äldre granskog med stort lövinslag intill bäck</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5356,7 +5356,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112678602</v>
+        <v>112678690</v>
       </c>
       <c r="B45" t="n">
         <v>77876</v>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527212</v>
+        <v>527260</v>
       </c>
       <c r="R45" t="n">
-        <v>7101308</v>
+        <v>7101099</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Äldre granskog med stort lövinslag intill bäck</t>
+          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5463,10 +5463,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112678690</v>
+        <v>112678679</v>
       </c>
       <c r="B46" t="n">
-        <v>77876</v>
+        <v>56641</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5479,21 +5479,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527260</v>
+        <v>527322</v>
       </c>
       <c r="R46" t="n">
-        <v>7101099</v>
+        <v>7101080</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5539,6 +5539,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Spår i gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5570,10 +5575,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112678679</v>
+        <v>112678613</v>
       </c>
       <c r="B47" t="n">
-        <v>56641</v>
+        <v>89814</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5586,21 +5591,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5610,10 +5615,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527322</v>
+        <v>527045</v>
       </c>
       <c r="R47" t="n">
-        <v>7101080</v>
+        <v>7101241</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5650,7 +5655,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Spår i gran</t>
+          <t>Strandskogen, utanför planerad hänsyn</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5664,7 +5669,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+          <t>Äldre barrskog vid sjöstrand med lövinslag och med en del död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5682,10 +5687,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112678613</v>
+        <v>112678696</v>
       </c>
       <c r="B48" t="n">
-        <v>89814</v>
+        <v>93477</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5694,25 +5699,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>2808</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grov husmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum pyrenaicum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spruce) M.Fleisch.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5722,10 +5727,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527045</v>
+        <v>527240</v>
       </c>
       <c r="R48" t="n">
-        <v>7101241</v>
+        <v>7101112</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5760,11 +5765,6 @@
           <t>2023-10-06</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Strandskogen, utanför planerad hänsyn</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Äldre barrskog vid sjöstrand med lövinslag och med en del död ved i olika nedbrytningsstadier</t>
+          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5794,10 +5794,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112678696</v>
+        <v>112678681</v>
       </c>
       <c r="B49" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5810,21 +5810,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2808</v>
+        <v>2809</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grov husmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hylocomiastrum pyrenaicum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spruce) M.Fleisch.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527240</v>
+        <v>527322</v>
       </c>
       <c r="R49" t="n">
-        <v>7101112</v>
+        <v>7101080</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112678681</v>
+        <v>112678694</v>
       </c>
       <c r="B50" t="n">
-        <v>93478</v>
+        <v>77876</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5913,25 +5913,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527322</v>
+        <v>527240</v>
       </c>
       <c r="R50" t="n">
-        <v>7101080</v>
+        <v>7101112</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6008,7 +6008,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112678694</v>
+        <v>112678699</v>
       </c>
       <c r="B51" t="n">
         <v>77876</v>
@@ -6048,10 +6048,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527240</v>
+        <v>527226</v>
       </c>
       <c r="R51" t="n">
-        <v>7101112</v>
+        <v>7101137</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6115,7 +6115,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112678699</v>
+        <v>112678704</v>
       </c>
       <c r="B52" t="n">
         <v>77876</v>
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527226</v>
+        <v>527223</v>
       </c>
       <c r="R52" t="n">
         <v>7101137</v>
@@ -6222,10 +6222,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112678704</v>
+        <v>112678702</v>
       </c>
       <c r="B53" t="n">
-        <v>77876</v>
+        <v>94896</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6234,25 +6234,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>990</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6262,7 +6262,7 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527223</v>
+        <v>527226</v>
       </c>
       <c r="R53" t="n">
         <v>7101137</v>
@@ -6306,6 +6306,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6329,10 +6330,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>112678702</v>
+        <v>112678703</v>
       </c>
       <c r="B54" t="n">
-        <v>94896</v>
+        <v>89810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6341,25 +6342,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>990</v>
+        <v>1204</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6413,13 +6414,17 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
           <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Granlåga, 15 cm</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6437,10 +6442,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>112678703</v>
+        <v>112678682</v>
       </c>
       <c r="B55" t="n">
-        <v>89810</v>
+        <v>89796</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6453,21 +6458,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6477,10 +6482,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527226</v>
+        <v>527322</v>
       </c>
       <c r="R55" t="n">
-        <v>7101137</v>
+        <v>7101080</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6527,11 +6532,6 @@
       <c r="AI55" t="inlineStr">
         <is>
           <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Granlåga, 15 cm</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6549,10 +6549,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>112678682</v>
+        <v>112678644</v>
       </c>
       <c r="B56" t="n">
-        <v>89796</v>
+        <v>93490</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6561,25 +6561,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>2813</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6589,13 +6589,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527322</v>
+        <v>527136</v>
       </c>
       <c r="R56" t="n">
-        <v>7101080</v>
+        <v>7101176</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6656,10 +6656,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>112678644</v>
+        <v>112678633</v>
       </c>
       <c r="B57" t="n">
-        <v>93490</v>
+        <v>94580</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6668,25 +6668,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2813</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>112678633</v>
+        <v>112678697</v>
       </c>
       <c r="B58" t="n">
-        <v>94580</v>
+        <v>95985</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6775,25 +6775,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6803,13 +6803,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527136</v>
+        <v>527226</v>
       </c>
       <c r="R58" t="n">
-        <v>7101176</v>
+        <v>7101137</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6870,10 +6870,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>112678697</v>
+        <v>112678710</v>
       </c>
       <c r="B59" t="n">
-        <v>95985</v>
+        <v>93478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6886,21 +6886,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>2809</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6910,10 +6910,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527226</v>
+        <v>527172</v>
       </c>
       <c r="R59" t="n">
-        <v>7101137</v>
+        <v>7101167</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6977,10 +6977,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>112678710</v>
+        <v>112678706</v>
       </c>
       <c r="B60" t="n">
-        <v>93478</v>
+        <v>77876</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6989,25 +6989,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7017,10 +7017,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527172</v>
+        <v>527205</v>
       </c>
       <c r="R60" t="n">
-        <v>7101167</v>
+        <v>7101146</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7084,7 +7084,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>112678706</v>
+        <v>112678686</v>
       </c>
       <c r="B61" t="n">
         <v>77876</v>
@@ -7124,10 +7124,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527205</v>
+        <v>527294</v>
       </c>
       <c r="R61" t="n">
-        <v>7101146</v>
+        <v>7101096</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7160,6 +7160,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Mycket riklig</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7191,10 +7196,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>112678686</v>
+        <v>113619287</v>
       </c>
       <c r="B62" t="n">
-        <v>77876</v>
+        <v>94181</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7207,34 +7212,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>771</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Platt spretmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Herzogiella turfacea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gårdsvattnet SO, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527294</v>
+        <v>527151</v>
       </c>
       <c r="R62" t="n">
-        <v>7101096</v>
+        <v>7101331</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7269,11 +7279,6 @@
           <t>2023-10-06</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Mycket riklig</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7285,7 +7290,22 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+          <t>Äldre barrskog vid sjöstrand med blöthål och med död ved i olika nedbrytningsstadier</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>På granstubbe och lövved i blöthål några meter innanför stranden</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>23-538</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7299,14 +7319,18 @@
           <t>Henrik Weibull</t>
         </is>
       </c>
-      <c r="AY62" t="inlineStr"/>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av mossor – eftersök i lämpliga miljöer</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>113619287</v>
+        <v>113619286</v>
       </c>
       <c r="B63" t="n">
-        <v>94181</v>
+        <v>94275</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7315,31 +7339,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>771</v>
+        <v>210</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Platt spretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Herzogiella turfacea</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Lindb.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>med groddkorn</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7386,6 +7410,11 @@
           <t>2023-10-06</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Protonema</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7398,21 +7427,6 @@
       <c r="AI63" t="inlineStr">
         <is>
           <t>Äldre barrskog vid sjöstrand med blöthål och med död ved i olika nedbrytningsstadier</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>På granstubbe och lövved i blöthål några meter innanför stranden</t>
-        </is>
-      </c>
-      <c r="AQ63" t="inlineStr">
-        <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>23-538</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7427,127 +7441,6 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av mossor – eftersök i lämpliga miljöer</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>113619286</v>
-      </c>
-      <c r="B64" t="n">
-        <v>94275</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>210</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Grön sköldmossa</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Buxbaumia viridis</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Gårdsvattnet SO, Jmt</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>527151</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7101331</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2023-10-06</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2023-10-06</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Protonema</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Äldre barrskog vid sjöstrand med blöthål och med död ved i olika nedbrytningsstadier</t>
-        </is>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
         <is>
           <t>Biogeografisk uppföljning av mossor – eftersök i lämpliga miljöer</t>
         </is>

--- a/artfynd/A 57844-2022 artfynd.xlsx
+++ b/artfynd/A 57844-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112678692</v>
+        <v>112678633</v>
       </c>
       <c r="B2" t="n">
-        <v>93478</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527240</v>
+        <v>527137</v>
       </c>
       <c r="R2" t="n">
-        <v>7101112</v>
+        <v>7101175</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112678601</v>
+        <v>112678701</v>
       </c>
       <c r="B3" t="n">
-        <v>95985</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527212</v>
+        <v>527226</v>
       </c>
       <c r="R3" t="n">
-        <v>7101308</v>
+        <v>7101137</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,11 +850,6 @@
           <t>2023-10-06</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Extrema mängder ar revlummer. Marktäckare.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -876,7 +861,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Äldre granskog med stort lövinslag intill bäck</t>
+          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -894,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112678669</v>
+        <v>112678595</v>
       </c>
       <c r="B4" t="n">
-        <v>93478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527236</v>
+        <v>527151</v>
       </c>
       <c r="R4" t="n">
-        <v>7101138</v>
+        <v>7101331</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,6 +952,11 @@
           <t>2023-10-06</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Protonema</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -983,7 +968,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+          <t>Äldre barrskog vid sjöstrand med blöthål och med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1001,37 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112678677</v>
+        <v>112678671</v>
       </c>
       <c r="B5" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527297</v>
+        <v>527236</v>
       </c>
       <c r="R5" t="n">
-        <v>7101113</v>
+        <v>7101138</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,6 +1059,11 @@
           <t>2023-10-06</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Protonema</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1091,6 +1076,21 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Murken granlåga</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>23-537</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1108,15 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112678665</v>
+        <v>112678598</v>
       </c>
       <c r="B6" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527202</v>
+        <v>527151</v>
       </c>
       <c r="R6" t="n">
-        <v>7101154</v>
+        <v>7101331</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1192,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+          <t>Äldre barrskog vid sjöstrand med blöthål och med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1215,15 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112678683</v>
+        <v>112678597</v>
       </c>
       <c r="B7" t="n">
-        <v>55852</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,34 +1221,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>771</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Platt spretmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Herzogiella turfacea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gårdsvattnet SO, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527294</v>
+        <v>527151</v>
       </c>
       <c r="R7" t="n">
-        <v>7101096</v>
+        <v>7101331</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1299,22 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+          <t>Äldre barrskog vid sjöstrand med blöthål och med död ved i olika nedbrytningsstadier</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>På granstubbe och lövved i blöthål några meter innanför stranden</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>23-538</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1322,37 +1332,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112678599</v>
+        <v>112678702</v>
       </c>
       <c r="B8" t="n">
-        <v>89814</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>990</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527153</v>
+        <v>527226</v>
       </c>
       <c r="R8" t="n">
-        <v>7101334</v>
+        <v>7101137</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,12 +1411,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre barrskog vid sjöstrand med lövinslag och med en del död ved i olika nedbrytningsstadier</t>
+          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1429,15 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112678715</v>
+        <v>112678615</v>
       </c>
       <c r="B9" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1446,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527096</v>
+        <v>527050</v>
       </c>
       <c r="R9" t="n">
-        <v>7101170</v>
+        <v>7101229</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1510,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Snitsel för SCA VÄG över bäcken.</t>
+          <t>Strandskogen, i kanten av planerad hänsyn</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,7 +1524,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+          <t>Äldre barrskog vid sjöstrand med lövinslag och med en del död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1541,15 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112678598</v>
+        <v>112678682</v>
       </c>
       <c r="B10" t="n">
-        <v>90077</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,21 +1553,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527150</v>
+        <v>527322</v>
       </c>
       <c r="R10" t="n">
-        <v>7101330</v>
+        <v>7101080</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1626,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre barrskog vid sjöstrand med blöthål och med död ved i olika nedbrytningsstadier</t>
+          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1648,37 +1644,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112678713</v>
+        <v>112678703</v>
       </c>
       <c r="B11" t="n">
-        <v>93478</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1688,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527096</v>
+        <v>527226</v>
       </c>
       <c r="R11" t="n">
-        <v>7101170</v>
+        <v>7101137</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,6 +1729,11 @@
       <c r="AI11" t="inlineStr">
         <is>
           <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Granlåga, 15 cm</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1755,37 +1751,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112678666</v>
+        <v>112678596</v>
       </c>
       <c r="B12" t="n">
-        <v>93478</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1786,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527202</v>
+        <v>527151</v>
       </c>
       <c r="R12" t="n">
-        <v>7101154</v>
+        <v>7101331</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1835,12 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+          <t>Äldre barrskog vid sjöstrand med blöthål och med död ved i olika nedbrytningsstadier</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Vid basen av nydöd gran, 15 cm.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1862,37 +1858,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112678698</v>
+        <v>112678628</v>
       </c>
       <c r="B13" t="n">
-        <v>93478</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>1841</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,13 +1893,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>527226</v>
+        <v>527137</v>
       </c>
       <c r="R13" t="n">
-        <v>7101137</v>
+        <v>7101175</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1969,15 +1960,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112678678</v>
+        <v>112678662</v>
       </c>
       <c r="B14" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,21 +1971,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1841</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2009,10 +1995,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527322</v>
+        <v>527047</v>
       </c>
       <c r="R14" t="n">
-        <v>7101080</v>
+        <v>7101183</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2076,15 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112678673</v>
+        <v>112678675</v>
       </c>
       <c r="B15" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,21 +2073,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1841</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2183,37 +2164,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112678663</v>
+        <v>112678689</v>
       </c>
       <c r="B16" t="n">
-        <v>93478</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2809</v>
+        <v>1841</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527186</v>
+        <v>527261</v>
       </c>
       <c r="R16" t="n">
-        <v>7101165</v>
+        <v>7101099</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2261,6 +2237,11 @@
           <t>2023-10-06</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Delvis utanför skyddszonen</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2273,6 +2254,11 @@
       <c r="AI16" t="inlineStr">
         <is>
           <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2290,15 +2276,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112678693</v>
+        <v>112678620</v>
       </c>
       <c r="B17" t="n">
-        <v>95977</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,21 +2287,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221944</v>
+        <v>2326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,13 +2311,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527240</v>
+        <v>527137</v>
       </c>
       <c r="R17" t="n">
-        <v>7101112</v>
+        <v>7101175</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2397,15 +2378,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112678620</v>
+        <v>112678646</v>
       </c>
       <c r="B18" t="n">
-        <v>95225</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96337</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,21 +2389,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2326</v>
+        <v>2808</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Grov husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Hylocomiastrum pyrenaicum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>(Spruce) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2437,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527136</v>
+        <v>527137</v>
       </c>
       <c r="R18" t="n">
-        <v>7101176</v>
+        <v>7101175</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2504,37 +2480,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112678615</v>
+        <v>112678696</v>
       </c>
       <c r="B19" t="n">
-        <v>89792</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96337</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>2808</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grov husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hylocomiastrum pyrenaicum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spruce) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527050</v>
+        <v>527240</v>
       </c>
       <c r="R19" t="n">
-        <v>7101228</v>
+        <v>7101112</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2582,11 +2553,6 @@
           <t>2023-10-06</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Strandskogen, i kanten av planerad hänsyn</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2598,7 +2564,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Äldre barrskog vid sjöstrand med lövinslag och med en del död ved i olika nedbrytningsstadier</t>
+          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2616,15 +2582,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112678595</v>
+        <v>112678607</v>
       </c>
       <c r="B20" t="n">
-        <v>93675</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,21 +2593,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>2809</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2617,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527150</v>
+        <v>527218</v>
       </c>
       <c r="R20" t="n">
-        <v>7101330</v>
+        <v>7101268</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,11 +2655,6 @@
           <t>2023-10-06</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Protonema</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2710,7 +2666,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Äldre barrskog vid sjöstrand med blöthål och med död ved i olika nedbrytningsstadier</t>
+          <t>Äldre granskog med stort lövinslag intill bäck</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2728,37 +2684,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112678701</v>
+        <v>112678645</v>
       </c>
       <c r="B21" t="n">
-        <v>94580</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>2809</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2768,13 +2719,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527226</v>
+        <v>527137</v>
       </c>
       <c r="R21" t="n">
-        <v>7101137</v>
+        <v>7101175</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2835,37 +2786,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112678705</v>
+        <v>112678663</v>
       </c>
       <c r="B22" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2875,10 +2821,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527223</v>
+        <v>527185</v>
       </c>
       <c r="R22" t="n">
-        <v>7101137</v>
+        <v>7101165</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2911,11 +2857,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-10-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spår i gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2947,37 +2888,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112678596</v>
+        <v>112678666</v>
       </c>
       <c r="B23" t="n">
-        <v>74065</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1467</v>
+        <v>2809</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2987,10 +2923,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527150</v>
+        <v>527202</v>
       </c>
       <c r="R23" t="n">
-        <v>7101330</v>
+        <v>7101154</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,12 +2972,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Äldre barrskog vid sjöstrand med blöthål och med död ved i olika nedbrytningsstadier</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Vid basen av nydöd gran, 15 cm.</t>
+          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3059,15 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112678685</v>
+        <v>112678669</v>
       </c>
       <c r="B24" t="n">
-        <v>93478</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3099,10 +3025,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527294</v>
+        <v>527236</v>
       </c>
       <c r="R24" t="n">
-        <v>7101096</v>
+        <v>7101138</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3166,37 +3092,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112678667</v>
+        <v>112678681</v>
       </c>
       <c r="B25" t="n">
-        <v>89814</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3206,10 +3127,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527202</v>
+        <v>527322</v>
       </c>
       <c r="R25" t="n">
-        <v>7101154</v>
+        <v>7101080</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3273,15 +3194,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112678695</v>
+        <v>112678685</v>
       </c>
       <c r="B26" t="n">
-        <v>89760</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,21 +3205,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3313,10 +3229,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527240</v>
+        <v>527294</v>
       </c>
       <c r="R26" t="n">
-        <v>7101112</v>
+        <v>7101096</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3380,37 +3296,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112678664</v>
+        <v>112678692</v>
       </c>
       <c r="B27" t="n">
-        <v>89814</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3420,10 +3331,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527186</v>
+        <v>527240</v>
       </c>
       <c r="R27" t="n">
-        <v>7101165</v>
+        <v>7101112</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3487,37 +3398,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112678680</v>
+        <v>112678698</v>
       </c>
       <c r="B28" t="n">
-        <v>74060</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3527,10 +3433,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527322</v>
+        <v>527226</v>
       </c>
       <c r="R28" t="n">
-        <v>7101080</v>
+        <v>7101137</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3594,15 +3500,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112678671</v>
+        <v>112678710</v>
       </c>
       <c r="B29" t="n">
-        <v>93675</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3610,21 +3511,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>210</v>
+        <v>2809</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3634,10 +3535,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527236</v>
+        <v>527173</v>
       </c>
       <c r="R29" t="n">
-        <v>7101138</v>
+        <v>7101167</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3672,11 +3573,6 @@
           <t>2023-10-06</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Protonema</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3689,21 +3585,6 @@
       <c r="AI29" t="inlineStr">
         <is>
           <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Murken granlåga</t>
-        </is>
-      </c>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>23-537</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3721,37 +3602,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112678689</v>
+        <v>112678713</v>
       </c>
       <c r="B30" t="n">
-        <v>94900</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1841</v>
+        <v>2809</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3761,10 +3637,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527260</v>
+        <v>527097</v>
       </c>
       <c r="R30" t="n">
-        <v>7101099</v>
+        <v>7101170</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3799,11 +3675,6 @@
           <t>2023-10-06</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Delvis utanför skyddszonen</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3816,11 +3687,6 @@
       <c r="AI30" t="inlineStr">
         <is>
           <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3838,15 +3704,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112678645</v>
+        <v>112678644</v>
       </c>
       <c r="B31" t="n">
-        <v>93478</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3854,21 +3715,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2809</v>
+        <v>2813</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3878,10 +3739,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527136</v>
+        <v>527137</v>
       </c>
       <c r="R31" t="n">
-        <v>7101176</v>
+        <v>7101175</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3945,37 +3806,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112678675</v>
+        <v>112678707</v>
       </c>
       <c r="B32" t="n">
-        <v>94900</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1841</v>
+        <v>2813</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3985,10 +3841,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527289</v>
+        <v>527205</v>
       </c>
       <c r="R32" t="n">
-        <v>7101110</v>
+        <v>7101145</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4052,55 +3908,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112678597</v>
+        <v>112678606</v>
       </c>
       <c r="B33" t="n">
-        <v>93596</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>771</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Platt spretmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Herzogiella turfacea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lindb.) Z.Iwats.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gårdsvattnet SO, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527150</v>
+        <v>527218</v>
       </c>
       <c r="R33" t="n">
-        <v>7101330</v>
+        <v>7101268</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4146,22 +3992,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Äldre barrskog vid sjöstrand med blöthål och med död ved i olika nedbrytningsstadier</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>På granstubbe och lövved i blöthål några meter innanför stranden</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>23-538</t>
+          <t>Äldre granskog med stort lövinslag intill bäck</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4179,37 +4010,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112678604</v>
+        <v>112678695</v>
       </c>
       <c r="B34" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4219,10 +4045,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527256</v>
+        <v>527240</v>
       </c>
       <c r="R34" t="n">
-        <v>7101242</v>
+        <v>7101112</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4268,7 +4094,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Äldre granskog med stort lövinslag intill bäck</t>
+          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4286,19 +4112,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112678668</v>
+        <v>112678602</v>
       </c>
       <c r="B35" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4326,10 +4147,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527236</v>
+        <v>527212</v>
       </c>
       <c r="R35" t="n">
-        <v>7101138</v>
+        <v>7101308</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4375,7 +4196,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+          <t>Äldre granskog med stort lövinslag intill bäck</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4393,19 +4214,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112678709</v>
+        <v>112678603</v>
       </c>
       <c r="B36" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4433,10 +4249,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>527172</v>
+        <v>527240</v>
       </c>
       <c r="R36" t="n">
-        <v>7101167</v>
+        <v>7101226</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4482,7 +4298,12 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+          <t>Äldre granskog med stort lövinslag intill bäck</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>på gran i halvöppet kärr</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4500,37 +4321,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112678707</v>
+        <v>112678604</v>
       </c>
       <c r="B37" t="n">
-        <v>93490</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4540,10 +4356,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527205</v>
+        <v>527256</v>
       </c>
       <c r="R37" t="n">
-        <v>7101146</v>
+        <v>7101242</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4589,7 +4405,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+          <t>Äldre granskog med stort lövinslag intill bäck</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4607,37 +4423,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112678628</v>
+        <v>112678612</v>
       </c>
       <c r="B38" t="n">
-        <v>94900</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1841</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4647,13 +4458,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527136</v>
+        <v>527046</v>
       </c>
       <c r="R38" t="n">
-        <v>7101176</v>
+        <v>7101241</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4696,7 +4507,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+          <t>Äldre barrskog vid sjöstrand med lövinslag och med en del död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4714,37 +4525,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112678606</v>
+        <v>112678661</v>
       </c>
       <c r="B39" t="n">
-        <v>89760</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4754,10 +4560,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527218</v>
+        <v>527047</v>
       </c>
       <c r="R39" t="n">
-        <v>7101268</v>
+        <v>7101183</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4803,7 +4609,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Äldre granskog med stort lövinslag intill bäck</t>
+          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4821,37 +4627,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112678712</v>
+        <v>112678665</v>
       </c>
       <c r="B40" t="n">
-        <v>104065</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4861,10 +4662,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527096</v>
+        <v>527202</v>
       </c>
       <c r="R40" t="n">
-        <v>7101170</v>
+        <v>7101154</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4928,19 +4729,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112678612</v>
+        <v>112678668</v>
       </c>
       <c r="B41" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4968,10 +4764,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527045</v>
+        <v>527236</v>
       </c>
       <c r="R41" t="n">
-        <v>7101241</v>
+        <v>7101138</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5017,7 +4813,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Äldre barrskog vid sjöstrand med lövinslag och med en del död ved i olika nedbrytningsstadier</t>
+          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5035,19 +4831,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112678711</v>
+        <v>112678673</v>
       </c>
       <c r="B42" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5075,10 +4866,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527144</v>
+        <v>527289</v>
       </c>
       <c r="R42" t="n">
-        <v>7101152</v>
+        <v>7101110</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5142,37 +4933,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112678607</v>
+        <v>112678677</v>
       </c>
       <c r="B43" t="n">
-        <v>93478</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5182,10 +4968,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527218</v>
+        <v>527297</v>
       </c>
       <c r="R43" t="n">
-        <v>7101268</v>
+        <v>7101112</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5231,7 +5017,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Äldre granskog med stort lövinslag intill bäck</t>
+          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5249,37 +5035,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112678646</v>
+        <v>112678678</v>
       </c>
       <c r="B44" t="n">
-        <v>93477</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2808</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grov husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hylocomiastrum pyrenaicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spruce) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5289,13 +5070,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527136</v>
+        <v>527322</v>
       </c>
       <c r="R44" t="n">
-        <v>7101176</v>
+        <v>7101080</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5356,19 +5137,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112678602</v>
+        <v>112678686</v>
       </c>
       <c r="B45" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5396,10 +5172,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527212</v>
+        <v>527294</v>
       </c>
       <c r="R45" t="n">
-        <v>7101308</v>
+        <v>7101096</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5434,6 +5210,11 @@
           <t>2023-10-06</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Mycket riklig</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5445,7 +5226,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Äldre granskog med stort lövinslag intill bäck</t>
+          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5466,16 +5247,11 @@
         <v>112678690</v>
       </c>
       <c r="B46" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5503,7 +5279,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527260</v>
+        <v>527261</v>
       </c>
       <c r="R46" t="n">
         <v>7101099</v>
@@ -5570,37 +5346,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112678679</v>
+        <v>112678691</v>
       </c>
       <c r="B47" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5610,10 +5381,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527322</v>
+        <v>527240</v>
       </c>
       <c r="R47" t="n">
-        <v>7101080</v>
+        <v>7101112</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5646,11 +5417,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-10-06</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Spår i gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5682,37 +5448,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112678613</v>
+        <v>112678699</v>
       </c>
       <c r="B48" t="n">
-        <v>89814</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5722,10 +5483,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527045</v>
+        <v>527226</v>
       </c>
       <c r="R48" t="n">
-        <v>7101241</v>
+        <v>7101137</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5760,11 +5521,6 @@
           <t>2023-10-06</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Strandskogen, utanför planerad hänsyn</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5776,7 +5532,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Äldre barrskog vid sjöstrand med lövinslag och med en del död ved i olika nedbrytningsstadier</t>
+          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5794,37 +5550,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112678696</v>
+        <v>112678704</v>
       </c>
       <c r="B49" t="n">
-        <v>93477</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2808</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grov husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hylocomiastrum pyrenaicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spruce) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5834,10 +5585,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527240</v>
+        <v>527223</v>
       </c>
       <c r="R49" t="n">
-        <v>7101112</v>
+        <v>7101137</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5901,37 +5652,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112678681</v>
+        <v>112678706</v>
       </c>
       <c r="B50" t="n">
-        <v>93478</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5941,10 +5687,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527322</v>
+        <v>527205</v>
       </c>
       <c r="R50" t="n">
-        <v>7101080</v>
+        <v>7101145</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6008,19 +5754,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112678694</v>
+        <v>112678709</v>
       </c>
       <c r="B51" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -6048,10 +5789,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527240</v>
+        <v>527173</v>
       </c>
       <c r="R51" t="n">
-        <v>7101112</v>
+        <v>7101167</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6115,19 +5856,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112678699</v>
+        <v>112678711</v>
       </c>
       <c r="B52" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -6155,10 +5891,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527226</v>
+        <v>527145</v>
       </c>
       <c r="R52" t="n">
-        <v>7101137</v>
+        <v>7101152</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6222,19 +5958,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112678704</v>
+        <v>112678715</v>
       </c>
       <c r="B53" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -6262,10 +5993,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527223</v>
+        <v>527097</v>
       </c>
       <c r="R53" t="n">
-        <v>7101137</v>
+        <v>7101170</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6298,6 +6029,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Snitsel för SCA VÄG över bäcken.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6329,37 +6065,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>112678702</v>
+        <v>112678680</v>
       </c>
       <c r="B54" t="n">
-        <v>94896</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>990</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6369,10 +6100,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527226</v>
+        <v>527322</v>
       </c>
       <c r="R54" t="n">
-        <v>7101137</v>
+        <v>7101080</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6413,7 +6144,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6437,15 +6167,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>112678703</v>
+        <v>112678679</v>
       </c>
       <c r="B55" t="n">
-        <v>89810</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6453,21 +6178,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6477,10 +6202,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527226</v>
+        <v>527322</v>
       </c>
       <c r="R55" t="n">
-        <v>7101137</v>
+        <v>7101080</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6515,6 +6240,11 @@
           <t>2023-10-06</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Spår i gran</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6527,11 +6257,6 @@
       <c r="AI55" t="inlineStr">
         <is>
           <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Granlåga, 15 cm</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6549,15 +6274,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>112678682</v>
+        <v>112678705</v>
       </c>
       <c r="B56" t="n">
-        <v>89796</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6565,21 +6285,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6589,10 +6309,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527322</v>
+        <v>527223</v>
       </c>
       <c r="R56" t="n">
-        <v>7101080</v>
+        <v>7101137</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6625,6 +6345,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Spår i gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6656,15 +6381,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>112678644</v>
+        <v>112678683</v>
       </c>
       <c r="B57" t="n">
-        <v>93490</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6672,21 +6392,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2813</v>
+        <v>102612</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6696,13 +6416,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527136</v>
+        <v>527294</v>
       </c>
       <c r="R57" t="n">
-        <v>7101176</v>
+        <v>7101096</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6763,37 +6483,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>112678633</v>
+        <v>112678712</v>
       </c>
       <c r="B58" t="n">
-        <v>94580</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>221725</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6803,13 +6518,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527136</v>
+        <v>527097</v>
       </c>
       <c r="R58" t="n">
-        <v>7101176</v>
+        <v>7101170</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6870,15 +6585,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>112678697</v>
+        <v>112678693</v>
       </c>
       <c r="B59" t="n">
-        <v>95985</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97977</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6886,23 +6596,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6910,10 +6616,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527226</v>
+        <v>527240</v>
       </c>
       <c r="R59" t="n">
-        <v>7101137</v>
+        <v>7101112</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6977,15 +6683,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>112678710</v>
+        <v>112678601</v>
       </c>
       <c r="B60" t="n">
-        <v>93478</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6993,21 +6694,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2809</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7017,10 +6718,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527172</v>
+        <v>527212</v>
       </c>
       <c r="R60" t="n">
-        <v>7101167</v>
+        <v>7101308</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7055,6 +6756,11 @@
           <t>2023-10-06</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Extrema mängder ar revlummer. Marktäckare.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7066,7 +6772,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
+          <t>Äldre granskog med stort lövinslag intill bäck</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7084,37 +6790,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>112678706</v>
+        <v>112678697</v>
       </c>
       <c r="B61" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7124,10 +6825,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527205</v>
+        <v>527226</v>
       </c>
       <c r="R61" t="n">
-        <v>7101146</v>
+        <v>7101137</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7188,370 +6889,6 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>112678686</v>
-      </c>
-      <c r="B62" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Gårdsvattnet SO, Jmt</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>527294</v>
-      </c>
-      <c r="R62" t="n">
-        <v>7101096</v>
-      </c>
-      <c r="S62" t="n">
-        <v>10</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2023-10-06</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2023-10-06</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Mycket riklig</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>Naturskogsartad granskog med bäck och andra fuktiga partier och rikligt med död ved i olika nedbrytningsstadier</t>
-        </is>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>113619287</v>
-      </c>
-      <c r="B63" t="n">
-        <v>94181</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>771</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Platt spretmossa</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Herzogiella turfacea</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Lindb.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Gårdsvattnet SO, Jmt</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>527151</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7101331</v>
-      </c>
-      <c r="S63" t="n">
-        <v>10</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2023-10-06</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2023-10-06</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>Äldre barrskog vid sjöstrand med blöthål och med död ved i olika nedbrytningsstadier</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>På granstubbe och lövved i blöthål några meter innanför stranden</t>
-        </is>
-      </c>
-      <c r="AQ63" t="inlineStr">
-        <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>23-538</t>
-        </is>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av mossor – eftersök i lämpliga miljöer</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>113619286</v>
-      </c>
-      <c r="B64" t="n">
-        <v>94275</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>210</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Grön sköldmossa</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Buxbaumia viridis</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Gårdsvattnet SO, Jmt</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>527151</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7101331</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2023-10-06</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2023-10-06</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Protonema</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Äldre barrskog vid sjöstrand med blöthål och med död ved i olika nedbrytningsstadier</t>
-        </is>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av mossor – eftersök i lämpliga miljöer</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57844-2022 artfynd.xlsx
+++ b/artfynd/A 57844-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678633</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678701</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678595</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678671</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678598</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678597</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1432,6 +1467,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678702</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1539,6 +1579,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678615</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1641,6 +1686,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678682</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1748,6 +1798,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678703</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1855,6 +1910,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678596</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1957,6 +2017,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678628</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2059,6 +2124,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678662</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2161,6 +2231,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678675</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2273,6 +2348,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678689</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2375,6 +2455,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678620</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2477,6 +2562,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678646</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2579,6 +2669,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678696</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2681,6 +2776,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678607</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2783,6 +2883,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678645</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2885,6 +2990,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678663</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2987,6 +3097,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678666</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3089,6 +3204,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678669</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3191,6 +3311,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678681</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3293,6 +3418,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678685</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3395,6 +3525,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678692</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3497,6 +3632,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678698</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3599,6 +3739,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678710</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3701,6 +3846,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678713</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3803,6 +3953,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678644</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3905,6 +4060,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678707</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4007,6 +4167,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678606</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4109,6 +4274,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678695</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4211,6 +4381,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678602</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4318,6 +4493,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678603</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4420,6 +4600,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678604</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4522,6 +4707,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678612</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4624,6 +4814,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678661</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4726,6 +4921,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678665</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4828,6 +5028,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678668</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4930,6 +5135,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678673</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5032,6 +5242,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678677</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5134,6 +5349,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678678</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5241,6 +5461,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678686</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5343,6 +5568,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678690</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5445,6 +5675,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678691</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5547,6 +5782,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678699</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5649,6 +5889,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678704</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5751,6 +5996,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678706</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5853,6 +6103,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678709</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5955,6 +6210,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678711</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6062,6 +6322,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678715</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6164,6 +6429,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678680</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6271,6 +6541,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678679</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6378,6 +6653,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678705</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6480,6 +6760,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678683</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6582,6 +6867,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678712</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6680,6 +6970,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678693</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6787,6 +7082,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678601</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6889,8 +7189,75 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678697</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 57844-2022 artfynd.xlsx
+++ b/artfynd/A 57844-2022 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>112678595</v>
       </c>
       <c r="B4" t="n">
-        <v>96554</v>
+        <v>96725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>112678671</v>
       </c>
       <c r="B5" t="n">
-        <v>96554</v>
+        <v>96725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57844-2022 artfynd.xlsx
+++ b/artfynd/A 57844-2022 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>112678595</v>
       </c>
       <c r="B4" t="n">
-        <v>96725</v>
+        <v>96726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>112678671</v>
       </c>
       <c r="B5" t="n">
-        <v>96725</v>
+        <v>96726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57844-2022 artfynd.xlsx
+++ b/artfynd/A 57844-2022 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>112678595</v>
       </c>
       <c r="B4" t="n">
-        <v>96726</v>
+        <v>96727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>112678671</v>
       </c>
       <c r="B5" t="n">
-        <v>96726</v>
+        <v>96727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57844-2022 artfynd.xlsx
+++ b/artfynd/A 57844-2022 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>112678595</v>
       </c>
       <c r="B4" t="n">
-        <v>96727</v>
+        <v>96733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>112678671</v>
       </c>
       <c r="B5" t="n">
-        <v>96727</v>
+        <v>96733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57844-2022 artfynd.xlsx
+++ b/artfynd/A 57844-2022 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>112678595</v>
       </c>
       <c r="B4" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>112678671</v>
       </c>
       <c r="B5" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57844-2022 artfynd.xlsx
+++ b/artfynd/A 57844-2022 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>112678595</v>
       </c>
       <c r="B4" t="n">
-        <v>96734</v>
+        <v>96745</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>112678671</v>
       </c>
       <c r="B5" t="n">
-        <v>96734</v>
+        <v>96745</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57844-2022 artfynd.xlsx
+++ b/artfynd/A 57844-2022 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>112678595</v>
       </c>
       <c r="B4" t="n">
-        <v>96745</v>
+        <v>96758</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>112678671</v>
       </c>
       <c r="B5" t="n">
-        <v>96745</v>
+        <v>96758</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57844-2022 artfynd.xlsx
+++ b/artfynd/A 57844-2022 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>112678595</v>
       </c>
       <c r="B4" t="n">
-        <v>96758</v>
+        <v>96759</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>112678671</v>
       </c>
       <c r="B5" t="n">
-        <v>96758</v>
+        <v>96759</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57844-2022 artfynd.xlsx
+++ b/artfynd/A 57844-2022 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>112678595</v>
       </c>
       <c r="B4" t="n">
-        <v>96759</v>
+        <v>96772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>112678671</v>
       </c>
       <c r="B5" t="n">
-        <v>96759</v>
+        <v>96772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57844-2022 artfynd.xlsx
+++ b/artfynd/A 57844-2022 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>112678595</v>
       </c>
       <c r="B4" t="n">
-        <v>96772</v>
+        <v>96773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>112678671</v>
       </c>
       <c r="B5" t="n">
-        <v>96772</v>
+        <v>96773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
